--- a/InputData/elec/MLfPPR/Min Life for Pwr Plnt Rtmnts.xlsx
+++ b/InputData/elec/MLfPPR/Min Life for Pwr Plnt Rtmnts.xlsx
@@ -1,34 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\MLfPPR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\MLfPPR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB91667-EBA9-4F50-8495-B1F237C9E919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA7C5469-9B83-49E8-84E0-DAD6D1CD82B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27720" yWindow="3885" windowWidth="28770" windowHeight="17370" xr2:uid="{67B50A2A-83E2-40E1-A966-DC033ADD8EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="MLfPPR" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>MLfPPR Minimum Lifetime for Power Plant Retirements</t>
   </si>
   <si>
-    <t>Iowa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sources: </t>
   </si>
   <si>
@@ -41,10 +51,10 @@
     <t>Lifetime</t>
   </si>
   <si>
+    <t>All Plants</t>
+  </si>
+  <si>
     <t>All years</t>
-  </si>
-  <si>
-    <t>All Plants</t>
   </si>
 </sst>
 </file>
@@ -404,7 +414,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B7A547-DAFD-4CBC-90C6-A86A1413C282}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -412,21 +422,18 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -435,7 +442,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{498B6747-53CF-4C1D-84DD-4D89524F3F28}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
@@ -444,7 +451,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
@@ -452,7 +459,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>20</v>
